--- a/Result KIDSFEST - CAT 1.xlsx
+++ b/Result KIDSFEST - CAT 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\TECHOSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1AB708D-8C41-43B2-855D-DF2D8ABBA1DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F446FBB-C78D-4546-AFD9-46BC55F2E511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="101" sheetId="3" r:id="rId1"/>
@@ -2232,7 +2232,9 @@
       <c r="F11" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="G11" s="36"/>
+      <c r="G11" s="36" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="12" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
@@ -2250,9 +2252,6 @@
       </c>
       <c r="F12" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="G12" s="36" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
